--- a/artfynd/A 46032-2023 artfynd.xlsx
+++ b/artfynd/A 46032-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 46032-2023 artfynd.xlsx
+++ b/artfynd/A 46032-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,6 +785,214 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124829132</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57692</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102623</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Trädlärka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lullula arborea</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ängen, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>563250</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6247689</v>
+      </c>
+      <c r="S3" t="n">
+        <v>50</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Frida Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124830240</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56621</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102932</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Kricka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Anas crecca</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ängen, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>563214</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6247689</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Torsås</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-04-17</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elin Jonsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Julia Odéhn</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 46032-2023 artfynd.xlsx
+++ b/artfynd/A 46032-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124829132</v>
+        <v>124830240</v>
       </c>
       <c r="B3" t="n">
-        <v>57692</v>
+        <v>56621</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,45 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102623</v>
+        <v>102932</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ängen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563250</v>
+        <v>563214</v>
       </c>
       <c r="R3" t="n">
         <v>6247689</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,12 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,17 +882,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Frida Gustafsson</t>
+          <t>Julia Odéhn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124830240</v>
+        <v>124829132</v>
       </c>
       <c r="B4" t="n">
-        <v>56621</v>
+        <v>57692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,41 +901,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102932</v>
+        <v>102623</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ängen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563214</v>
+        <v>563250</v>
       </c>
       <c r="R4" t="n">
         <v>6247689</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,12 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,7 +988,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Julia Odéhn</t>
+          <t>Frida Gustafsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 46032-2023 artfynd.xlsx
+++ b/artfynd/A 46032-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124830240</v>
+        <v>124829132</v>
       </c>
       <c r="B3" t="n">
-        <v>56621</v>
+        <v>57692</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102932</v>
+        <v>102623</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ängen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563214</v>
+        <v>563250</v>
       </c>
       <c r="R3" t="n">
         <v>6247689</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,17 +886,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Julia Odéhn</t>
+          <t>Frida Gustafsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124829132</v>
+        <v>124830240</v>
       </c>
       <c r="B4" t="n">
-        <v>57692</v>
+        <v>56621</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,45 +905,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102623</v>
+        <v>102932</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ängen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563250</v>
+        <v>563214</v>
       </c>
       <c r="R4" t="n">
         <v>6247689</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,12 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,7 +988,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Frida Gustafsson</t>
+          <t>Julia Odéhn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 46032-2023 artfynd.xlsx
+++ b/artfynd/A 46032-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124829132</v>
+        <v>124830240</v>
       </c>
       <c r="B3" t="n">
-        <v>57692</v>
+        <v>56796</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,45 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102623</v>
+        <v>102932</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ängen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563250</v>
+        <v>563214</v>
       </c>
       <c r="R3" t="n">
         <v>6247689</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,12 +857,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,17 +882,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Frida Gustafsson</t>
+          <t>Julia Odéhn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124830240</v>
+        <v>124829132</v>
       </c>
       <c r="B4" t="n">
-        <v>56621</v>
+        <v>57806</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -905,41 +901,45 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102932</v>
+        <v>102623</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ängen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563214</v>
+        <v>563250</v>
       </c>
       <c r="R4" t="n">
         <v>6247689</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,12 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,7 +988,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Julia Odéhn</t>
+          <t>Frida Gustafsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 46032-2023 artfynd.xlsx
+++ b/artfynd/A 46032-2023 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124830240</v>
+        <v>124829132</v>
       </c>
       <c r="B3" t="n">
-        <v>56796</v>
+        <v>57806</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,41 +799,45 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102932</v>
+        <v>102623</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ängen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563214</v>
+        <v>563250</v>
       </c>
       <c r="R3" t="n">
         <v>6247689</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,12 +861,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -882,17 +886,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Julia Odéhn</t>
+          <t>Frida Gustafsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124829132</v>
+        <v>124830240</v>
       </c>
       <c r="B4" t="n">
-        <v>57806</v>
+        <v>56796</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -901,45 +905,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102623</v>
+        <v>102932</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ängen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563250</v>
+        <v>563214</v>
       </c>
       <c r="R4" t="n">
         <v>6247689</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,12 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,7 +988,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Frida Gustafsson</t>
+          <t>Julia Odéhn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 46032-2023 artfynd.xlsx
+++ b/artfynd/A 46032-2023 artfynd.xlsx
@@ -787,57 +787,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124829132</v>
+        <v>124830240</v>
       </c>
       <c r="B3" t="n">
-        <v>57806</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56796</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102623</v>
+        <v>102932</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Kricka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Anas crecca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ängen, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563250</v>
+        <v>563214</v>
       </c>
       <c r="R3" t="n">
         <v>6247689</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -861,12 +852,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-17</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,60 +877,59 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Frida Gustafsson</t>
+          <t>Julia Odéhn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124830240</v>
+        <v>124829132</v>
       </c>
       <c r="B4" t="n">
-        <v>56796</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57806</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102932</v>
+        <v>102623</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kricka</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Anas crecca</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ängen, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563214</v>
+        <v>563250</v>
       </c>
       <c r="R4" t="n">
         <v>6247689</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,12 +953,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-17</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -988,7 +978,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Julia Odéhn</t>
+          <t>Frida Gustafsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
